--- a/data/trans_orig/P37A$otros-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37A$otros-Clase-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363013</t>
+          <t>362578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365350</t>
+          <t>366103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731361</t>
+          <t>731289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>738033</t>
+          <t>738032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537043</t>
+          <t>536236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>703134</t>
+          <t>704048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1232122</t>
+          <t>1231436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947413</t>
+          <t>1947380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561635</t>
+          <t>562200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>912674</t>
+          <t>911048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1243805</t>
+          <t>1244767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1542003</t>
+          <t>1541805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3261326</t>
+          <t>3261100</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3269314</t>
+          <t>3269313</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3368058</t>
+          <t>3368111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3377133</t>
+          <t>3377135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6632743</t>
+          <t>6633542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6644715</t>
+          <t>6644803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309776</t>
+          <t>309747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746998</t>
+          <t>746988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331992</t>
+          <t>330527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>749887</t>
+          <t>750577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624595</t>
+          <t>624591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>884710</t>
+          <t>885622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1154190</t>
+          <t>1154183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>761512</t>
+          <t>761422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919521</t>
+          <t>1918807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>754996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1266242</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1104276</t>
+          <t>1103738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1370764</t>
+          <t>1371147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3415004</t>
+          <t>3415129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3537888</t>
+          <t>3537849</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3548169</t>
+          <t>3548181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6957301</t>
+          <t>6957143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6969036</t>
+          <t>6968887</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422095</t>
+          <t>420160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>342606</t>
+          <t>342560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>768904</t>
+          <t>768018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369420</t>
+          <t>371526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>743614</t>
+          <t>743450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158742</t>
+          <t>158814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678329</t>
+          <t>679261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1139633</t>
+          <t>1139531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148846</t>
+          <t>1148849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>818704</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1961963</t>
+          <t>1962689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973474</t>
+          <t>1973722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615381</t>
+          <t>615400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>730482</t>
+          <t>730485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737320</t>
+          <t>737319</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349334</t>
+          <t>1349000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1357950</t>
+          <t>1357951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275445</t>
+          <t>275396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286047</t>
+          <t>285566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070815</t>
+          <t>1070835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1081089</t>
+          <t>1081010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1350683</t>
+          <t>1351657</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364588</t>
+          <t>1365070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>35530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3363287</t>
+          <t>3363643</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379286</t>
+          <t>3379140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3511032</t>
+          <t>3510387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3525579</t>
+          <t>3525270</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6880881</t>
+          <t>6881788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6901862</t>
+          <t>6903287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,22 +8668,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500387</t>
+          <t>544816</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494497</t>
+          <t>538389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503447</t>
+          <t>548557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>440742</t>
+          <t>481460</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>435794</t>
+          <t>475084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444229</t>
+          <t>484905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>941129</t>
+          <t>1026277</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>933354</t>
+          <t>1017379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946271</t>
+          <t>1031123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>445871</t>
+          <t>476412</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439135</t>
+          <t>469122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449888</t>
+          <t>480566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>381253</t>
+          <t>421245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378474</t>
+          <t>418092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382420</t>
+          <t>422587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>827124</t>
+          <t>897658</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819642</t>
+          <t>889780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831232</t>
+          <t>902030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>663558</t>
+          <t>465881</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656455</t>
+          <t>458958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667955</t>
+          <t>469728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165503</t>
+          <t>185379</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>181499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166745</t>
+          <t>186883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>829062</t>
+          <t>651259</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>821731</t>
+          <t>644097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833702</t>
+          <t>655616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>27058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1027394</t>
+          <t>1124185</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1019186</t>
+          <t>1115326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1031935</t>
+          <t>1129078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>969906</t>
+          <t>852839</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>961957</t>
+          <t>844835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>974671</t>
+          <t>856910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1997298</t>
+          <t>1977024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1986145</t>
+          <t>1965996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2004484</t>
+          <t>1983586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>471254</t>
+          <t>564007</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465721</t>
+          <t>558277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474063</t>
+          <t>566870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>833647</t>
+          <t>822527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>827857</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>837501</t>
+          <t>826193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1304902</t>
+          <t>1386534</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1295868</t>
+          <t>1379095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1309382</t>
+          <t>1391489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>752474</t>
+          <t>835452</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>741910</t>
+          <t>824932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757462</t>
+          <t>840519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>992981</t>
+          <t>1072680</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>982095</t>
+          <t>1062234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>997923</t>
+          <t>1077820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>41883</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49654</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61324</t>
+          <t>66438</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>84363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3348970</t>
+          <t>3412529</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3336340</t>
+          <t>3400593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3358669</t>
+          <t>3422746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3543525</t>
+          <t>3598902</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3528104</t>
+          <t>3585533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3553681</t>
+          <t>3608846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6892494</t>
+          <t>7011431</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6873591</t>
+          <t>6993506</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6906716</t>
+          <t>7025436</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
